--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/MICHIGAN_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/MICHIGAN_2022.xlsx
@@ -499,7 +499,7 @@
         <v>4</v>
       </c>
       <c r="D8">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="9">
@@ -751,7 +751,7 @@
         <v>4</v>
       </c>
       <c r="D22">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="23">
@@ -823,7 +823,7 @@
         <v>4</v>
       </c>
       <c r="D26">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="27">
@@ -985,7 +985,7 @@
         <v>4</v>
       </c>
       <c r="D35">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="36">
@@ -1471,7 +1471,7 @@
         <v>4</v>
       </c>
       <c r="D62">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="63">
@@ -1507,7 +1507,7 @@
         <v>4</v>
       </c>
       <c r="D64">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="65">
@@ -1561,7 +1561,7 @@
         <v>4</v>
       </c>
       <c r="D67">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="68">
@@ -1669,7 +1669,7 @@
         <v>4</v>
       </c>
       <c r="D73">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="74">
@@ -2335,7 +2335,7 @@
         <v>4</v>
       </c>
       <c r="D110">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="111">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C120">
@@ -2659,7 +2659,7 @@
         <v>4</v>
       </c>
       <c r="D128">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="129">
@@ -3541,7 +3541,7 @@
         <v>4</v>
       </c>
       <c r="D177">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="178">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C186">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C193">
@@ -4171,7 +4171,7 @@
         <v>4</v>
       </c>
       <c r="D212">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="213">
@@ -4693,7 +4693,7 @@
         <v>4</v>
       </c>
       <c r="D241">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="242">
@@ -4783,7 +4783,7 @@
         <v>4</v>
       </c>
       <c r="D246">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="247">
@@ -4819,7 +4819,7 @@
         <v>4</v>
       </c>
       <c r="D248">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="249">
@@ -4873,7 +4873,7 @@
         <v>4</v>
       </c>
       <c r="D251">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="252">
@@ -4927,7 +4927,7 @@
         <v>4</v>
       </c>
       <c r="D254">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="255">
@@ -4999,7 +4999,7 @@
         <v>4</v>
       </c>
       <c r="D258">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="259">
@@ -5125,7 +5125,7 @@
         <v>4</v>
       </c>
       <c r="D265">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="266">
@@ -5377,7 +5377,7 @@
         <v>4</v>
       </c>
       <c r="D279">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="280">
@@ -5485,7 +5485,7 @@
         <v>4</v>
       </c>
       <c r="D285">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="286">
@@ -5773,7 +5773,7 @@
         <v>4</v>
       </c>
       <c r="D301">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="302">
@@ -5917,7 +5917,7 @@
         <v>4</v>
       </c>
       <c r="D309">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="310">
@@ -6745,7 +6745,7 @@
         <v>4</v>
       </c>
       <c r="D355">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="356">
@@ -7015,7 +7015,7 @@
         <v>4</v>
       </c>
       <c r="D370">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="371">
@@ -7411,7 +7411,7 @@
         <v>4</v>
       </c>
       <c r="D392">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="393">
@@ -7861,7 +7861,7 @@
         <v>4</v>
       </c>
       <c r="D417">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="418">
@@ -8023,7 +8023,7 @@
         <v>4</v>
       </c>
       <c r="D426">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="427">
@@ -8077,7 +8077,7 @@
         <v>4</v>
       </c>
       <c r="D429">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="430">
@@ -8203,7 +8203,7 @@
         <v>4</v>
       </c>
       <c r="D436">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="437">
@@ -8545,7 +8545,7 @@
         <v>4</v>
       </c>
       <c r="D455">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="456">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>General Trevino</t>
+          <t>Gral. Trevino</t>
         </is>
       </c>
       <c r="C479">
@@ -9373,7 +9373,7 @@
         <v>4</v>
       </c>
       <c r="D501">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="502">
@@ -9463,7 +9463,7 @@
         <v>4</v>
       </c>
       <c r="D506">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="507">
@@ -9841,7 +9841,7 @@
         <v>4</v>
       </c>
       <c r="D527">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="528">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C543">
@@ -10399,7 +10399,7 @@
         <v>4</v>
       </c>
       <c r="D558">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="559">
@@ -10471,7 +10471,7 @@
         <v>4</v>
       </c>
       <c r="D562">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="563">
@@ -10543,7 +10543,7 @@
         <v>4</v>
       </c>
       <c r="D566">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="567">
@@ -10705,7 +10705,7 @@
         <v>4</v>
       </c>
       <c r="D575">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="576">
@@ -10957,7 +10957,7 @@
         <v>4</v>
       </c>
       <c r="D589">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="590">
@@ -10993,7 +10993,7 @@
         <v>4</v>
       </c>
       <c r="D591">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="592">
@@ -11029,7 +11029,7 @@
         <v>4</v>
       </c>
       <c r="D593">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="594">
@@ -11821,7 +11821,7 @@
         <v>4</v>
       </c>
       <c r="D637">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="638">
@@ -12001,7 +12001,7 @@
         <v>4</v>
       </c>
       <c r="D647">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="648">
@@ -12019,7 +12019,7 @@
         <v>4</v>
       </c>
       <c r="D648">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="649">
@@ -12685,7 +12685,7 @@
         <v>4</v>
       </c>
       <c r="D685">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="686">
@@ -13135,7 +13135,7 @@
         <v>4</v>
       </c>
       <c r="D710">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="711">
@@ -13153,7 +13153,7 @@
         <v>4</v>
       </c>
       <c r="D711">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="712">
@@ -13189,7 +13189,7 @@
         <v>4</v>
       </c>
       <c r="D713">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="714">
@@ -13567,7 +13567,7 @@
         <v>4</v>
       </c>
       <c r="D734">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="735">
@@ -13729,7 +13729,7 @@
         <v>4</v>
       </c>
       <c r="D743">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="744">
@@ -13747,7 +13747,7 @@
         <v>4</v>
       </c>
       <c r="D744">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="745">
@@ -14359,7 +14359,7 @@
         <v>4</v>
       </c>
       <c r="D778">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="779">
@@ -14395,7 +14395,7 @@
         <v>4</v>
       </c>
       <c r="D780">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="781">
@@ -14791,7 +14791,7 @@
         <v>4</v>
       </c>
       <c r="D802">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="803">
@@ -15277,7 +15277,7 @@
         <v>4</v>
       </c>
       <c r="D829">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="830">
@@ -15313,7 +15313,7 @@
         <v>4</v>
       </c>
       <c r="D831">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="832">
@@ -15637,7 +15637,7 @@
         <v>4</v>
       </c>
       <c r="D849">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="850">
@@ -15745,7 +15745,7 @@
         <v>4</v>
       </c>
       <c r="D855">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="856">
@@ -16015,7 +16015,7 @@
         <v>4</v>
       </c>
       <c r="D870">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="871">
@@ -16051,7 +16051,7 @@
         <v>4</v>
       </c>
       <c r="D872">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="873">
@@ -16087,7 +16087,7 @@
         <v>4</v>
       </c>
       <c r="D874">
-        <v>0.0009521542489883361</v>
+        <v>0.000952154248988336</v>
       </c>
     </row>
     <row r="875">
